--- a/output/pdf_financials_xlsx/AE.xlsx
+++ b/output/pdf_financials_xlsx/AE.xlsx
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.752109</v>
+        <v>-3.752109</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>7.854685</v>
+        <v>-7.854685</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-12.412196</v>
@@ -962,16 +962,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.752109</v>
+        <v>-3.752109</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.854685</v>
+        <v>-7.854685</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-12.412196</v>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.752109</v>
+        <v>-3.752109</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.854685</v>
+        <v>-7.854685</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-12.412196</v>
@@ -1120,16 +1120,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>53.601557</v>
+        <v>-53.601557</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>66.00792</v>
+        <v>-66.00792</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>84.21553299999999</v>
+        <v>-84.21553299999999</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-130.911417</v>
+        <v>130.911417</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>177.317086</v>
@@ -1147,16 +1147,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.752109</v>
+        <v>-3.752109</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.854685</v>
+        <v>-7.854685</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-12.412196</v>
@@ -1201,16 +1201,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.752109</v>
+        <v>-3.752109</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.854685</v>
+        <v>-7.854685</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-12.412196</v>
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.309075</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.724066</v>
       </c>
     </row>
     <row r="93">
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-7.854685</v>
@@ -5104,7 +5104,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -10492,13 +10496,13 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>5.052932</v>
+        <v>-5.052932</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>7.854685</v>
+        <v>-7.854685</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -10939,10 +10943,10 @@
         </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>3.752109</v>
+        <v>-3.752109</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>3.300396</v>
+        <v>-3.300396</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AE.xlsx
+++ b/output/pdf_financials_xlsx/AE.xlsx
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.29229</v>
+        <v>3.752109</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.370779</v>
+        <v>3.300396</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.509207</v>
+        <v>6.263732</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.757983</v>
+        <v>10.841414</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>14.461237</v>
       </c>
     </row>
     <row r="11">
@@ -697,16 +697,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.29229</v>
+        <v>-3.752109</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.370779</v>
+        <v>-3.300396</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.509207</v>
+        <v>-6.263732</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.757983</v>
+        <v>-10.841414</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -729,16 +729,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008858</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.13958</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.483758</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.8866039999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1150,16 +1150,16 @@
         <v>-3.752109</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.300396</v>
+        <v>-3.291538</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.052932</v>
+        <v>-4.913352</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.854685</v>
+        <v>-7.370927</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-12.412196</v>
+        <v>-11.525592</v>
       </c>
     </row>
     <row r="28">
@@ -1204,16 +1204,16 @@
         <v>-3.752109</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.300396</v>
+        <v>-3.291538</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.052932</v>
+        <v>-4.913352</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.854685</v>
+        <v>-7.370927</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-12.412196</v>
+        <v>-11.525592</v>
       </c>
     </row>
     <row r="30">
@@ -1336,19 +1336,19 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.901307</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.706651</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.393661</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>35.929619</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>22.855361</v>
       </c>
     </row>
     <row r="35">
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.901307</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.706651</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.393661</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>35.929619</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>22.855361</v>
       </c>
     </row>
     <row r="37">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.316314</v>
+        <v>0.415007</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.713859</v>
+        <v>0.007208</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.4389</v>
+        <v>0.045239</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>35.996945</v>
+        <v>0.067326</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>22.982234</v>
+        <v>0.126873</v>
       </c>
     </row>
     <row r="49">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4512,7 +4512,11 @@
           <t>Reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -5330,7 +5334,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -6956,7 +6964,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -9686,7 +9698,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9862,7 +9874,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
